--- a/human_resources_forms/003_workplace_climate_audit_form--human_resources_forms.xlsx
+++ b/human_resources_forms/003_workplace_climate_audit_form--human_resources_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -888,12 +888,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>work_phone</t>
+          <t>work_phone_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Work Phone</t>
+          <t>Work Phone 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -934,12 +934,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>email_2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Email 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -957,12 +957,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>workplace_climate_score</t>
+          <t>workplace_climate_score_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Workplace Climate Score</t>
+          <t>Workplace Climate Score 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -985,7 +985,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Overall Satisfaction</t>
+          <t>Overall Satisfaction (2)</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>climate_survey</t>
+          <t>climate_survey_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Climate Survey</t>
+          <t>Climate Survey 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1098,12 +1098,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:C25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1148,29 +1148,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>overall_satisfaction_page_choices</t>
+          <t>climate_audit_form_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Very satisfied</t>
         </is>
       </c>
     </row>
@@ -1199,29 +1199,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>climate_survey_choices</t>
+          <t>overall_satisfaction_page_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>dissatisfied</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Dissatisfied</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1250,29 +1250,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>overall_climate_choices</t>
+          <t>climate_survey_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1301,80 +1301,80 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>climate_survey_choices</t>
+          <t>overall_climate_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>climate_survey_choices</t>
+          <t>climate_survey_2_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>climate_survey_choices</t>
+          <t>climate_survey_2_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>climate_satisfaction_choices</t>
+          <t>climate_survey_2_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Very satisfied</t>
         </is>
       </c>
     </row>
@@ -1403,29 +1403,29 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>work_place_climate_choices</t>
+          <t>climate_satisfaction_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>dissatisfied</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Dissatisfied</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1454,29 +1454,29 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>overall_climate_satisfaction_choices</t>
+          <t>work_place_climate_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Very satisfied</t>
         </is>
       </c>
     </row>
@@ -1505,12 +1505,29 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Neutral</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>overall_climate_satisfaction_choices</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>dissatisfied</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Dissatisfied</t>
         </is>
       </c>
     </row>
